--- a/analysis/开发人维度/贺蓉晖_sku_report.xlsx
+++ b/analysis/开发人维度/贺蓉晖_sku_report.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="汇总" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="25年06月" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="26年03月" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="25年07月" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="26年03月" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,70 +447,75 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>总结算销售额</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>总利润率</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>总可用库存</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>存活率</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>存活sku销售量</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>存活sku销售额</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存活SKU数</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>留存SKU总利润</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>留存SKU利润率</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淘汰SKU销售量</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>淘汰SKU销售额</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>淘汰SKU总数</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>淘汰率</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>淘汰SKU总利润</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>淘汰SKU利润率</t>
         </is>
@@ -525,46 +531,46 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="D2" t="n">
-        <v>1995.63</v>
+        <v>2537.07</v>
       </c>
       <c r="E2" t="n">
-        <v>447.36</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>22.42%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>587.55</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2061.57</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>28.50%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>135</v>
-      </c>
       <c r="J2" t="n">
-        <v>1995.63</v>
+        <v>175</v>
       </c>
       <c r="K2" t="n">
+        <v>2537.07</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>447.36</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>22.42%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>587.55</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>28.50%</t>
+        </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -572,15 +578,18 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -589,69 +598,146 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>206.37</v>
       </c>
       <c r="E3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>-1.88</v>
+      </c>
+      <c r="F3" t="n">
+        <v>173.73</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-1.08%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>32</v>
+      </c>
+      <c r="P3" t="n">
+        <v>206.37</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>-1.08%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>30</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
@@ -668,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,10 +790,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>总结算销售额</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>总可用库存</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>最新标签</t>
         </is>
@@ -730,18 +821,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="E2" t="n">
-        <v>1995.63</v>
+        <v>2537.07</v>
       </c>
       <c r="F2" t="n">
-        <v>447.36</v>
+        <v>587.55</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>2061.571768976023</v>
+      </c>
+      <c r="H2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
@@ -758,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,10 +888,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>总结算销售额</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>总可用库存</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>最新标签</t>
         </is>
@@ -806,6 +905,104 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>B0FGCPWB7D</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2270348</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AM-Yehao-UK</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2" t="n">
+        <v>206.37</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="G2" t="n">
+        <v>173.73</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>欧洲精铺2025淘汰</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>总销量</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>总销售额</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>总结算利润</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>总结算销售额</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>总可用库存</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>最新标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>B0GG9VYDCV</t>
         </is>
       </c>
@@ -826,12 +1023,15 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-2</v>
+        <v>-2.78</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>30</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>欧洲精铺2025</t>
         </is>
